--- a/test-automation.xlsx
+++ b/test-automation.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Bugs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Verification" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Coverage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="API Tests" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -525,7 +526,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Total Test Cases</t>
+          <t>Total Test Cases (UI E2E)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -535,7 +536,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PASS (Chromium)</t>
+          <t>PASS (Chromium UI)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -545,7 +546,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>FAIL (Chromium)</t>
+          <t>FAIL (Chromium UI)</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -555,7 +556,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>PASS (WebKit)</t>
+          <t>PASS (WebKit UI)</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -565,7 +566,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>FAIL (WebKit)</t>
+          <t>FAIL (WebKit UI)</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -575,64 +576,84 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>Total API Test Cases</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bugs Found</t>
+          <t>PASS (API)</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Critical Bugs</t>
+          <t>FAIL (API)</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Coverage (Modules)</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Storefront, Auth, Cart, Checkout, Admin, RBAC</t>
-        </is>
+          <t>Bugs Found</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Environments</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Chromium (Desktop Chrome), WebKit (Desktop Safari)</t>
-        </is>
+          <t>Critical Bugs</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Coverage (Modules)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Storefront, Auth, Cart, Checkout, Admin, RBAC, REST API</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Environments</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Chromium (UI), WebKit (UI), API request context</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>App URL</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>http://localhost:3000</t>
         </is>
@@ -1865,7 +1886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2009,20 +2030,42 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>npx playwright test --project=api</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>API Tests</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>40/40 ผ่าน (request context)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
           <t>npm run db:seed</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>seed สำเร็จก่อนรันเทสต์</t>
         </is>
@@ -2271,4 +2314,1544 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>API-AUTH-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>POST /auth/register</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>ลงทะเบียนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>201 + user + ไม่ leak hash</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>API-AUTH-002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>POST /auth/register</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>email ซ้ำ</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>API-AUTH-003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>POST /auth/register</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>ข้อมูลไม่ valid</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>API-AUTH-004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>POST /auth/login</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>login สำเร็จ</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>200 + user</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>API-AUTH-005</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>POST /auth/login</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>รหัสผิด</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>API-AUTH-006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>GET /auth/me</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>ไม่มี session</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>user null</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>API-AUTH-007</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>GET /auth/me</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>มี session</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>คืน user</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>API-AUTH-008</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>POST /auth/logout</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>logout แล้ว me null</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>API-AUTH-009</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>register→me (context)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>session cookie ทำงาน</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>me ไม่ null</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-001</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>GET /products</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>รายการ + pagination</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-002</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>GET /products?category</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>กรองหมวด</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>เฉพาะหมวด</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-003</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>GET /products?search</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ค้นหาภาษาไทย</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>ผลมีคำค้น</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-004</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>GET /products?min/max</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>กรองราคา</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>ช่วงราคาถูก</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-005</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>GET /products/[slug]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>รายละเอียด + reviews</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-006</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>GET /products/[slug]</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ไม่มีสินค้า</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-007</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>POST /products</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>ไม่มี session</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-008</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>POST /products</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>admin สำเร็จ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-009</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>POST /products</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ข้อมูลไม่ valid</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>API-PRD-010</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>POST /products</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>API-CAT-001</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>GET /categories</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>รายการ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>API-CAT-002</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>POST /categories</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ไม่มี session</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>API-CAT-002b</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>POST /categories</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>API-CAT-003</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>POST /categories</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>admin สำเร็จ + ซ้ำ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>201/409</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>API-CART-001</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>GET /cart</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ไม่ login</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>API-CART-002</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>POST /cart</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>เพิ่มสินค้า</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>200 + itemCount</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>API-CART-003</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>POST /cart</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>เกินสต็อก</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>API-CART-004</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>PATCH /cart/[id]</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>เปลี่ยนจำนวน</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>API-CART-005</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>DELETE /cart/[id]</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ลบ item</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>200 + ว่าง</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>API-ORD-001</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>POST /orders</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ไม่ login</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>API-ORD-002</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>POST /orders</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>checkout สำเร็จ + ลด stock</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>201 + ORD-</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>API-ORD-003</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>POST /orders</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>ไม่มี session</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>API-ORD-003b</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>POST /orders</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>body ไม่ valid</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>API-ORD-004</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>GET /orders</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>เห็นเฉพาะของตัวเอง</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>เฉพาะ user</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>API-ADM-001</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>PATCH /orders</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>ไม่มี session</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>API-ADM-001b</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>PATCH /orders</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>API-ADM-002</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>PATCH /orders</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>status ไม่ valid</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>API-ADM-003</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>GET /orders?scope=all</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>admin เห็นทั้งหมด</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>API-ADM-004</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>GET /admin/stats</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>ไม่มี session</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>API-ADM-005</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>GET /admin/stats</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>API-ADM-006</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>GET /admin/stats</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>200 + stats</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/test-automation.xlsx
+++ b/test-automation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Verification" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Coverage" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="API Tests" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Robot Tests" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -107,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,6 +126,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -657,6 +660,46 @@
         <is>
           <t>http://localhost:3000</t>
         </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Robot Framework Tests</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Robot PASS</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Robot FAIL</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Robot Bugs Found</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3854,4 +3897,739 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Bug ID</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>RF-STORE-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>หน้าแรก + สินค้าแนะนำ</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>RF-STORE-002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>CTA → /shop</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>RF-STORE-003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>เปิดสินค้า + รายละเอียด</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>RF-STORE-004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>ค้นหา กาแฟ</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>RF-AUTH-001</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>สมัครสมาชิก + เข้าสู่ระบบ</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>RF-AUTH-002</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>สมัครรหัสไม่ตรง → error</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>RF-AUTH-003</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>login seed customer</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>RF-AUTH-004</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>login รหัสผิด → error</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>RF-AUTH-005</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>logout ผ่าน UI</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>BUG-ROBOT-001</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>ใช้ JS click workaround (native click ไม่เปิด dropdown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>RF-AUTH-006</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Auth/RBAC</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>customer → /admin redirect</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>RF-CART-001</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>เพิ่มสินค้า → badge</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>RF-CART-002</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>/cart เปลี่ยนจำนวน</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>RF-CART-003</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ลบสินค้า → ว่าง</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>RF-CHK-001</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>สั่งซื้อ COD สำเร็จ → ORD-</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>RF-CHK-002</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ไม่กรอกที่อยู่ → validation</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Selenium</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>RF-API-001</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>API/Auth</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>register 201 ไม่ leak hash</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Requests</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>RF-API-002</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>API/Auth</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>register ซ้ำ 409</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Requests</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>RF-API-003</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>API/Auth</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>login 200</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Requests</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>RF-API-004</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>API/Auth</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>login รหัสผิด 401</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Requests</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>RF-API-005</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>API/Products</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>GET products + pagination</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Requests</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>RF-API-006</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>API/Products</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>กรองหมวด drinks</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Requests</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>RF-API-007</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>API/Security</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>GET cart ไม่ login → 401</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Requests</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>RF-API-008</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>API/RBAC</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>customer → admin/stats 403</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Robot+Requests</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>